--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y70"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | symbol-only separator/garbage line :: 29 ，</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BEVERLYâ€™S APPEAL.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: isolated marker/symbol line :: =</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -708,12 +712,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, June 29.â€”F. MacKelcan, Q.</t>
+          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ECKERT.—In Brantford, € nt., on the 28th inst,</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -799,12 +803,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CowiE.â€” In his city, on the 29th inst., Marion</t>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+5E97 CJK UNIFIED IDEOGRAPH-5E97 | isolated marker/symbol line :: 店</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: happy couple left on the 4 oâ€™clock train</t>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • One kiss before we part." "Wha—wha</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -832,7 +836,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L791: line starts with digit/letter garbage token | suspicious token(s): 1one (letter/digit mix) :: 1one or two gentlemen, in private family ;</t>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • One kiss before we part." "Wha—wha</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -858,12 +862,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -886,12 +890,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: Ï� x-</t>
+          <t>L290: stray/suspicious non-ASCII glyph(s): U+771F CJK UNIFIED IDEOGRAPH-771F | isolated marker/symbol line :: 真</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: best wishes of a large circle of friends.â€”</t>
+          <t>L1195: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -919,7 +923,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L840: line starts with digit/letter garbage token | suspicious token(s): 1Pianoforte (letter/digit mix) :: 1Pianoforte tuner, 146 Hannah street east.</t>
+          <t>L791: line starts with digit/letter garbage token | suspicious token(s): 1one (letter/digit mix) :: 1one or two gentlemen, in private family ;</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -973,14 +977,10 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: IN HYMENâ€™S BONDS.</t>
-        </is>
-      </c>
+          <t>L310: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -1002,7 +1002,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L862: line starts with digit/letter garbage token | suspicious token(s): 1RS (letter/digit mix) :: 1RS. REECE, NO. 190 JAMES STREET</t>
+          <t>L840: line starts with digit/letter garbage token | suspicious token(s): 1Pianoforte (letter/digit mix) :: 1Pianoforte tuner, 146 Hannah street east.</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1056,14 +1056,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pink crÃ©pon gowns and the maids of</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: umarried at the residence of the brideâ€™s</t>
-        </is>
-      </c>
+          <t>L376: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1085,7 +1081,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L1214: line starts with digit/letter garbage token | suspicious token(s): 1It (letter/digit mix) :: 1It is said that the most noted shot</t>
+          <t>L862: line starts with digit/letter garbage token | suspicious token(s): 1RS (letter/digit mix) :: 1RS. REECE, NO. 190 JAMES STREET</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1139,14 +1135,10 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: RENTâ€”M.RYMOND.,</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00AC NOT SIGN :: ECKERT.â€”In Brantford, â‚¬ nt., on the 28th inst,</t>
-        </is>
-      </c>
+          <t>L575: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1166,7 +1158,11 @@
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L1214: line starts with digit/letter garbage token | suspicious token(s): 1It (letter/digit mix) :: 1It is said that the most noted shot</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr">
@@ -1212,12 +1208,12 @@
           <t>L780: suspicious token(s): 50c (letter/digit mix) :: Straw Hats from 50c.</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: STOVE-TOWERS.â€”On June 28th, 1891. at the</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: Village Farm, b.h.， Rex Americas.</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1261,12 +1257,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1283,12 +1279,12 @@
           <t>L784: suspicious token(s): 25c (letter/digit mix) :: New Ties from 25c.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LOWE-BUTLER.â€”At the residence 9 of the bride's</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>L619: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: crack ， is. by Leland. he by Ham</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1337,7 +1333,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1354,17 +1350,17 @@
           <t>L791: line starts with digit/letter garbage token | suspicious token(s): 1one (letter/digit mix) :: 1one or two gentlemen, in private family ;</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L333: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SCOTT.â€”At the residence of his brother-in-law,</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 1</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | symbol-only separator/garbage line :: 29 ，</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1403,12 +1399,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1425,17 +1421,17 @@
           <t>L840: line starts with digit/letter garbage token | suspicious token(s): 1Pianoforte (letter/digit mix) :: 1Pianoforte tuner, 146 Hannah street east.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: on arrival of 8 oâ€™clock train from Hamilton.</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L58: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1455,7 +1451,7 @@
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr">
         <is>
-          <t>L597: abbreviation/spacing may be garbled :: Village Farm, b.h.ï¼Œ Rex Americas.</t>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: Village Farm, b.h.， Rex Americas.</t>
         </is>
       </c>
       <c r="W12" s="1" t="inlineStr">
@@ -1496,17 +1492,17 @@
           <t>L849: suspicious token(s): 10c (letter/digit mix) :: gloves cleaned, from 5? to 10c per pair. Feather-</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MCMAHON.â€”On June 29th, at No. 92 Isabella</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>L985: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L274: symbol-only separator/garbage line :: 0808080808</t>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1567,22 +1563,22 @@
           <t>L862: line starts with digit/letter garbage token | suspicious token(s): 1RS (letter/digit mix) :: 1RS. REECE, NO. 190 JAMES STREET</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cowie.â€”In this city, on the 29th inst., Marion</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>L990: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS, U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ）：</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L275: symbol-only separator/garbage line :: 08080</t>
+          <t>L274: symbol-only separator/garbage line :: 0808080808</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L1244: symbol-only separator/garbage line :: 82.60.</t>
+          <t>L1195: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1638,22 +1634,22 @@
           <t>L1066: suspicious token(s): 62c (letter/digit mix) :: as it was bought at 62c. on the dollar.</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HELP WANTEDâ€”MALE.</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>L991: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L280: symbol-only separator/garbage line :: 808080808808080880808088</t>
+          <t>L275: symbol-only separator/garbage line :: 08080</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L1265: isolated marker/symbol line :: *</t>
+          <t>L1244: symbol-only separator/garbage line :: 82.60.</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1705,20 +1701,24 @@
           <t>L1100: suspicious token(s): Geneva1 (letter/digit mix) :: Salesmen wanted. Apply Geneva1 Agent,City.</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L447: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Beverly and East Flamboroâ€™ be raised $2</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>L992: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L281: symbol-only separator/garbage line :: 8808080808080808888888888888088808</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr"/>
+          <t>L280: symbol-only separator/garbage line :: 808080808808080880808088</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>L1265: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
           <t>L1214: line starts with digit/letter garbage token | suspicious token(s): 1It (letter/digit mix) :: 1It is said that the most noted shot</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE TRADERSâ€™ BANK OF CANADA.</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>L1063: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: rar,Q.C.，of Hamilton:</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L282: symbol-only separator/garbage line :: 080808080808</t>
+          <t>L281: symbol-only separator/garbage line :: 8808080808080808888888888888088808</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr"/>
@@ -1815,17 +1815,17 @@
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ain grocery, fruit or confectionerâ€™s. Best</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>L1084: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L284: symbol-only separator/garbage line :: 88080803888808880808083</t>
+          <t>L282: symbol-only separator/garbage line :: 080808080808</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1862,17 +1862,17 @@
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock.</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>L1128: stray/suspicious non-ASCII glyph(s): U+5C11 CJK UNIFIED IDEOGRAPH-5C11 | isolated marker/symbol line :: 少</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L285: isolated marker/symbol line :: 8</t>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+5E97 CJK UNIFIED IDEOGRAPH-5E97 | isolated marker/symbol line :: 店</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr"/>
@@ -1910,16 +1910,12 @@
       </c>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ginning at 10 oâ€™clock in the morning.</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L286: isolated marker/symbol line :: 08</t>
+          <t>L284: symbol-only separator/garbage line :: 88080803888808880808083</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1957,16 +1953,12 @@
       </c>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mondayâ€™s match race is attracting</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L288: isolated marker/symbol line :: '</t>
+          <t>L285: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1978,7 +1970,7 @@
       <c r="U21" s="1" t="inlineStr"/>
       <c r="V21" s="1" t="inlineStr">
         <is>
-          <t>L1063: abbreviation/spacing may be garbled :: rar,Q.C.ï¼Œof Hamilton:</t>
+          <t>L1063: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: rar,Q.C.，of Hamilton:</t>
         </is>
       </c>
       <c r="W21" s="1" t="inlineStr">
@@ -2004,16 +1996,12 @@
       </c>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: King, dam Minnequa Maid, by Woodâ€™s</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L293: isolated marker/symbol line :: L</t>
+          <t>L286: isolated marker/symbol line :: 08</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -2047,16 +2035,12 @@
       </c>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York. June 29.â€”The weather at</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L294: isolated marker/symbol line :: T</t>
+          <t>L288: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -2090,16 +2074,12 @@
       </c>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: presents were magnificent. The brideâ€™s</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L309: isolated marker/symbol line :: 1</t>
+          <t>L290: stray/suspicious non-ASCII glyph(s): U+771F CJK UNIFIED IDEOGRAPH-771F | isolated marker/symbol line :: 真</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -2133,16 +2113,12 @@
       </c>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tions- Cowen, Leoncavalloâ€™s ** Berceuse,</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L293: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -2172,16 +2148,12 @@
       </c>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Sullivanâ€™s symphonies, in fact all the</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: B</t>
+          <t>L294: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -2207,16 +2179,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ One kiss before we part." "Whaâ€”wha</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L329: isolated marker/symbol line :: W</t>
+          <t>L309: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -2242,16 +2210,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”what ?" faltered the clerk, who ex-</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L333: isolated marker/symbol line :: L</t>
+          <t>L310: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2277,16 +2241,12 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: pected anything but that. *â€˜One kiss</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L337: isolated marker/symbol line :: 0</t>
+          <t>L320: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2312,16 +2272,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: before we part,â€™ repeated the pretty pure</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: 1</t>
+          <t>L329: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -2347,16 +2303,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”the Countess complained on account of</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: T</t>
+          <t>L333: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -2382,16 +2334,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of fruit jars and rubbers.â€”Hazell &amp; Son,</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L365: isolated marker/symbol line :: W</t>
+          <t>L337: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -2417,16 +2365,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WAUGHâ€™S,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L380: symbol-only separator/garbage line :: 1819, 58</t>
+          <t>L345: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2452,16 +2396,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L795: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 1 (shaded) park grounds, Elâ€™s nore, bay side,</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L397: symbol-only separator/garbage line :: .$ 1, 000, 000</t>
+          <t>L357: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2487,16 +2427,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: TRY KELLYâ€™S NEW MIXED HARD-</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L399: symbol-only separator/garbage line :: 600, 000</t>
+          <t>L365: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2522,16 +2458,12 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜Phone 1078. Office at râ€™amiltonâ€™s drug store.</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L401: symbol-only separator/garbage line :: 4, 900, 000</t>
+          <t>L376: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2557,16 +2489,12 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L847: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gentsâ€™ suit- ceaned this week, $1.25 dyed $1.75,</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L417: symbol-only separator/garbage line :: $1.00.</t>
+          <t>L380: symbol-only separator/garbage line :: 1819, 58</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2592,16 +2520,12 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L863: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: IVE north, has a large assortment of ladiesâ€™</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L397: symbol-only separator/garbage line :: .$ 1, 000, 000</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2627,16 +2551,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and childrenâ€™s spring dn s es for sale, new and</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L651: symbol-only separator/garbage line :: $400:</t>
+          <t>L399: symbol-only separator/garbage line :: 600, 000</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2662,16 +2582,12 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜0 and 52 James street north.</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L718: isolated marker/symbol line :: 0</t>
+          <t>L401: symbol-only separator/garbage line :: 4, 900, 000</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2697,16 +2613,12 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L933: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 1047.</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L725: isolated marker/symbol line :: E</t>
+          <t>L417: symbol-only separator/garbage line :: $1.00.</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2732,16 +2644,12 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L937: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Orangeville, June 29.-The second dayâ€™s</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L738: isolated marker/symbol line :: D</t>
+          <t>L575: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2767,16 +2675,12 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: money and J. W. Rattenburyâ€™s Hamlet</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L750: isolated marker/symbol line :: .</t>
+          <t>L651: symbol-only separator/garbage line :: $400:</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2802,16 +2706,12 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L988: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: aid Smithâ€™s place. After dinner, in the</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L759: isolated marker/symbol line :: V</t>
+          <t>L718: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2837,16 +2737,12 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1034: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: weâ€™ve got it. Frederick Lyonde, opposite</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L768: isolated marker/symbol line :: -</t>
+          <t>L725: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2872,16 +2768,12 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1088: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: trees. American Plum, Plantersâ€™ Pride Pear,</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L771: isolated marker/symbol line :: M</t>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2907,16 +2799,12 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Menâ€™s singlesâ€”H. R. Barnard beat P.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L788: isolated marker/symbol line :: 0</t>
+          <t>L738: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2942,16 +2830,12 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1195: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L790: isolated marker/symbol line :: S</t>
+          <t>L750: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2977,16 +2861,12 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1224: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: limited number of pupils; own or pupilsâ€™ resi-</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L791: isolated marker/symbol line :: P</t>
+          <t>L759: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3012,16 +2892,12 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1239: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: King street east, centre of Coppâ€™s block.</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L807: isolated marker/symbol line :: 1.,</t>
+          <t>L768: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3047,16 +2923,12 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CLINEâ€™S JUBILEE PARK.</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L829: isolated marker/symbol line :: A</t>
+          <t>L771: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3082,16 +2954,12 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Dick Hicksâ€”Sometimes I wish I was</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L856: isolated marker/symbol line :: A</t>
+          <t>L788: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3117,16 +2985,12 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: samples. Studio, 181 King cast, Coppâ€™s</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L888: isolated marker/symbol line :: h</t>
+          <t>L790: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3157,7 +3021,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line :: 82.60.</t>
+          <t>L791: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3188,7 +3052,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L987: symbol-only separator/garbage line :: 4111</t>
+          <t>L807: isolated marker/symbol line :: 1.,</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3219,7 +3083,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L993: symbol-only separator/garbage line :: 1223</t>
+          <t>L829: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3250,7 +3114,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L996: isolated marker/symbol line :: .</t>
+          <t>L856: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3281,7 +3145,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L997: symbol-only separator/garbage line :: 2 454</t>
+          <t>L888: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3312,7 +3176,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L1008: isolated marker/symbol line :: 7.</t>
+          <t>L921: symbol-only separator/garbage line :: 82.60.</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3343,7 +3207,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L1012: symbol-only separator/garbage line :: 11.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3374,7 +3238,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L1017: isolated marker/symbol line :: a</t>
+          <t>L985: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3405,7 +3269,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L1018: isolated marker/symbol line :: 8</t>
+          <t>L987: symbol-only separator/garbage line :: 4111</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3436,7 +3300,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L1037: isolated marker/symbol line :: 8.</t>
+          <t>L990: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS, U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ）：</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3467,7 +3331,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L1064: isolated marker/symbol line :: +</t>
+          <t>L991: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3498,7 +3362,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L1124: isolated marker/symbol line :: 2</t>
+          <t>L992: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3529,7 +3393,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L1125: isolated marker/symbol line :: V</t>
+          <t>L993: symbol-only separator/garbage line :: 1223</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3560,7 +3424,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L1126: isolated marker/symbol line :: b</t>
+          <t>L996: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3591,7 +3455,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L1127: isolated marker/symbol line :: X</t>
+          <t>L997: symbol-only separator/garbage line :: 2 454</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3622,7 +3486,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L1128: isolated marker/symbol line :: å°‘</t>
+          <t>L1008: isolated marker/symbol line :: 7.</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3653,7 +3517,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L1129: isolated marker/symbol line :: 7</t>
+          <t>L1012: symbol-only separator/garbage line :: 11.</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3668,6 +3532,347 @@
       <c r="X70" s="1" t="inlineStr"/>
       <c r="Y70" s="1" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr"/>
+      <c r="C71" s="1" t="inlineStr"/>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr"/>
+      <c r="F71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr"/>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
+      <c r="L71" s="1" t="inlineStr"/>
+      <c r="M71" s="1" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>L1017: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr"/>
+      <c r="R71" s="1" t="inlineStr"/>
+      <c r="S71" s="1" t="inlineStr"/>
+      <c r="T71" s="1" t="inlineStr"/>
+      <c r="U71" s="1" t="inlineStr"/>
+      <c r="V71" s="1" t="inlineStr"/>
+      <c r="W71" s="1" t="inlineStr"/>
+      <c r="X71" s="1" t="inlineStr"/>
+      <c r="Y71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr"/>
+      <c r="B72" s="1" t="inlineStr"/>
+      <c r="C72" s="1" t="inlineStr"/>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr"/>
+      <c r="F72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr"/>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
+      <c r="L72" s="1" t="inlineStr"/>
+      <c r="M72" s="1" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>L1018: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr"/>
+      <c r="P72" s="1" t="inlineStr"/>
+      <c r="Q72" s="1" t="inlineStr"/>
+      <c r="R72" s="1" t="inlineStr"/>
+      <c r="S72" s="1" t="inlineStr"/>
+      <c r="T72" s="1" t="inlineStr"/>
+      <c r="U72" s="1" t="inlineStr"/>
+      <c r="V72" s="1" t="inlineStr"/>
+      <c r="W72" s="1" t="inlineStr"/>
+      <c r="X72" s="1" t="inlineStr"/>
+      <c r="Y72" s="1" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr"/>
+      <c r="B73" s="1" t="inlineStr"/>
+      <c r="C73" s="1" t="inlineStr"/>
+      <c r="D73" s="1" t="inlineStr"/>
+      <c r="E73" s="1" t="inlineStr"/>
+      <c r="F73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr"/>
+      <c r="H73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr"/>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
+      <c r="L73" s="1" t="inlineStr"/>
+      <c r="M73" s="1" t="inlineStr"/>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>L1037: isolated marker/symbol line :: 8.</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr"/>
+      <c r="P73" s="1" t="inlineStr"/>
+      <c r="Q73" s="1" t="inlineStr"/>
+      <c r="R73" s="1" t="inlineStr"/>
+      <c r="S73" s="1" t="inlineStr"/>
+      <c r="T73" s="1" t="inlineStr"/>
+      <c r="U73" s="1" t="inlineStr"/>
+      <c r="V73" s="1" t="inlineStr"/>
+      <c r="W73" s="1" t="inlineStr"/>
+      <c r="X73" s="1" t="inlineStr"/>
+      <c r="Y73" s="1" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr"/>
+      <c r="B74" s="1" t="inlineStr"/>
+      <c r="C74" s="1" t="inlineStr"/>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr"/>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
+      <c r="L74" s="1" t="inlineStr"/>
+      <c r="M74" s="1" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>L1064: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr"/>
+      <c r="R74" s="1" t="inlineStr"/>
+      <c r="S74" s="1" t="inlineStr"/>
+      <c r="T74" s="1" t="inlineStr"/>
+      <c r="U74" s="1" t="inlineStr"/>
+      <c r="V74" s="1" t="inlineStr"/>
+      <c r="W74" s="1" t="inlineStr"/>
+      <c r="X74" s="1" t="inlineStr"/>
+      <c r="Y74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="1" t="inlineStr"/>
+      <c r="C75" s="1" t="inlineStr"/>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr"/>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
+      <c r="L75" s="1" t="inlineStr"/>
+      <c r="M75" s="1" t="inlineStr"/>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>L1084: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr"/>
+      <c r="R75" s="1" t="inlineStr"/>
+      <c r="S75" s="1" t="inlineStr"/>
+      <c r="T75" s="1" t="inlineStr"/>
+      <c r="U75" s="1" t="inlineStr"/>
+      <c r="V75" s="1" t="inlineStr"/>
+      <c r="W75" s="1" t="inlineStr"/>
+      <c r="X75" s="1" t="inlineStr"/>
+      <c r="Y75" s="1" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr"/>
+      <c r="B76" s="1" t="inlineStr"/>
+      <c r="C76" s="1" t="inlineStr"/>
+      <c r="D76" s="1" t="inlineStr"/>
+      <c r="E76" s="1" t="inlineStr"/>
+      <c r="F76" s="1" t="inlineStr"/>
+      <c r="G76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr"/>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
+      <c r="L76" s="1" t="inlineStr"/>
+      <c r="M76" s="1" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>L1124: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O76" s="1" t="inlineStr"/>
+      <c r="P76" s="1" t="inlineStr"/>
+      <c r="Q76" s="1" t="inlineStr"/>
+      <c r="R76" s="1" t="inlineStr"/>
+      <c r="S76" s="1" t="inlineStr"/>
+      <c r="T76" s="1" t="inlineStr"/>
+      <c r="U76" s="1" t="inlineStr"/>
+      <c r="V76" s="1" t="inlineStr"/>
+      <c r="W76" s="1" t="inlineStr"/>
+      <c r="X76" s="1" t="inlineStr"/>
+      <c r="Y76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr"/>
+      <c r="B77" s="1" t="inlineStr"/>
+      <c r="C77" s="1" t="inlineStr"/>
+      <c r="D77" s="1" t="inlineStr"/>
+      <c r="E77" s="1" t="inlineStr"/>
+      <c r="F77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr"/>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
+      <c r="L77" s="1" t="inlineStr"/>
+      <c r="M77" s="1" t="inlineStr"/>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>L1125: isolated marker/symbol line :: V</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr"/>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr"/>
+      <c r="R77" s="1" t="inlineStr"/>
+      <c r="S77" s="1" t="inlineStr"/>
+      <c r="T77" s="1" t="inlineStr"/>
+      <c r="U77" s="1" t="inlineStr"/>
+      <c r="V77" s="1" t="inlineStr"/>
+      <c r="W77" s="1" t="inlineStr"/>
+      <c r="X77" s="1" t="inlineStr"/>
+      <c r="Y77" s="1" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr"/>
+      <c r="B78" s="1" t="inlineStr"/>
+      <c r="C78" s="1" t="inlineStr"/>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr"/>
+      <c r="G78" s="1" t="inlineStr"/>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr"/>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
+      <c r="L78" s="1" t="inlineStr"/>
+      <c r="M78" s="1" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>L1126: isolated marker/symbol line :: b</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr"/>
+      <c r="R78" s="1" t="inlineStr"/>
+      <c r="S78" s="1" t="inlineStr"/>
+      <c r="T78" s="1" t="inlineStr"/>
+      <c r="U78" s="1" t="inlineStr"/>
+      <c r="V78" s="1" t="inlineStr"/>
+      <c r="W78" s="1" t="inlineStr"/>
+      <c r="X78" s="1" t="inlineStr"/>
+      <c r="Y78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr"/>
+      <c r="B79" s="1" t="inlineStr"/>
+      <c r="C79" s="1" t="inlineStr"/>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr"/>
+      <c r="F79" s="1" t="inlineStr"/>
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr"/>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="inlineStr"/>
+      <c r="M79" s="1" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>L1127: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr"/>
+      <c r="R79" s="1" t="inlineStr"/>
+      <c r="S79" s="1" t="inlineStr"/>
+      <c r="T79" s="1" t="inlineStr"/>
+      <c r="U79" s="1" t="inlineStr"/>
+      <c r="V79" s="1" t="inlineStr"/>
+      <c r="W79" s="1" t="inlineStr"/>
+      <c r="X79" s="1" t="inlineStr"/>
+      <c r="Y79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr"/>
+      <c r="C80" s="1" t="inlineStr"/>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr"/>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
+      <c r="L80" s="1" t="inlineStr"/>
+      <c r="M80" s="1" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>L1128: stray/suspicious non-ASCII glyph(s): U+5C11 CJK UNIFIED IDEOGRAPH-5C11 | isolated marker/symbol line :: 少</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr"/>
+      <c r="R80" s="1" t="inlineStr"/>
+      <c r="S80" s="1" t="inlineStr"/>
+      <c r="T80" s="1" t="inlineStr"/>
+      <c r="U80" s="1" t="inlineStr"/>
+      <c r="V80" s="1" t="inlineStr"/>
+      <c r="W80" s="1" t="inlineStr"/>
+      <c r="X80" s="1" t="inlineStr"/>
+      <c r="Y80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr"/>
+      <c r="C81" s="1" t="inlineStr"/>
+      <c r="D81" s="1" t="inlineStr"/>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr"/>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
+      <c r="L81" s="1" t="inlineStr"/>
+      <c r="M81" s="1" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>L1129: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr"/>
+      <c r="R81" s="1" t="inlineStr"/>
+      <c r="S81" s="1" t="inlineStr"/>
+      <c r="T81" s="1" t="inlineStr"/>
+      <c r="U81" s="1" t="inlineStr"/>
+      <c r="V81" s="1" t="inlineStr"/>
+      <c r="W81" s="1" t="inlineStr"/>
+      <c r="X81" s="1" t="inlineStr"/>
+      <c r="Y81" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
